--- a/results/pirate_sobel_noisy_binary_otsu_magnorm/qced_results_pirate_noisy.xlsx
+++ b/results/pirate_sobel_noisy_binary_otsu_magnorm/qced_results_pirate_noisy.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="raw" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +522,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261006_123150</t>
+          <t>20261007_084202</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>7771.02</v>
+        <v>4559.41</v>
       </c>
       <c r="M2" t="n">
         <v>0.5542482571306709</v>
@@ -592,6 +593,4834 @@
         <is>
           <t>inf</t>
         </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H3" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4567.43</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.554191521890619</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46.58861976163014</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9944095612189636</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.004667435601691657</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23.30921665456634</v>
+      </c>
+      <c r="R3" t="n">
+        <v>99.53325643983084</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9811701203623279</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H4" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4613.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5542388857350539</v>
+      </c>
+      <c r="N4" t="n">
+        <v>46.58861976163014</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9944043296215683</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.004402153018069973</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23.56334865519966</v>
+      </c>
+      <c r="R4" t="n">
+        <v>99.559784698193</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9820709957252243</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H5" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4592.97</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5542410483648116</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.47789311803152</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.994403407727532</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.004482891195693964</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23.48441801772877</v>
+      </c>
+      <c r="R5" t="n">
+        <v>99.5517108804306</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.9816965967600151</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H6" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4598.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5542396141207708</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.64859669357939</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.9943993330857043</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.004525182622068435</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>23.44363889352438</v>
+      </c>
+      <c r="R6" t="n">
+        <v>99.54748173779315</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9816050636868016</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H7" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4638.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5542263154495867</v>
+      </c>
+      <c r="N7" t="n">
+        <v>46.44521337946944</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9943954961549002</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.004598231449442522</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.37409172543481</v>
+      </c>
+      <c r="R7" t="n">
+        <v>99.54017685505575</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.9814037379108748</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4613.91</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5542288798178585</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46.49019607843137</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9943931012180097</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.004436755094194541</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>23.5293454337616</v>
+      </c>
+      <c r="R8" t="n">
+        <v>99.55632449058055</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.982008107265357</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4582.82</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5541892578875913</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46.50826605151865</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9944009947810399</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.004605920799692426</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23.3668353414258</v>
+      </c>
+      <c r="R9" t="n">
+        <v>99.53940792003075</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.9814159841151651</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4555.18</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5542327733023357</v>
+      </c>
+      <c r="N10" t="n">
+        <v>46.61437908496733</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.9944005674987262</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.004655901576316801</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23.31996209052821</v>
+      </c>
+      <c r="R10" t="n">
+        <v>99.53440984236832</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.9812262615301139</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H11" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4563.33</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5542354916077951</v>
+      </c>
+      <c r="N11" t="n">
+        <v>46.63590926566705</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9943901314853383</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.004605920799692426</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23.3668353414258</v>
+      </c>
+      <c r="R11" t="n">
+        <v>99.53940792003075</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.9814131008160859</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H12" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>512</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4491.22</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.554263767240965</v>
+      </c>
+      <c r="N12" t="n">
+        <v>45.81122645136486</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9928705647097784</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.006286043829296425</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.01622595199568</v>
+      </c>
+      <c r="R12" t="n">
+        <v>99.37139561707036</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.9745291395990092</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H13" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>512</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4496.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5542189978013264</v>
+      </c>
+      <c r="N13" t="n">
+        <v>45.65897731641676</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.9928944000705353</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.006163014225297962</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>22.10206829841728</v>
+      </c>
+      <c r="R13" t="n">
+        <v>99.3836985774702</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.9749550816342474</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H14" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>512</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4517.22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5541978220516147</v>
+      </c>
+      <c r="N14" t="n">
+        <v>45.74702037677817</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.99291101101817</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.006101499423298731</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22.14563425441025</v>
+      </c>
+      <c r="R14" t="n">
+        <v>99.38985005767013</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.9751980871114445</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H15" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>512</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4528.88</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.554209235930892</v>
+      </c>
+      <c r="N15" t="n">
+        <v>45.57631680123029</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.9928844231346832</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.006089965397923875</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>22.15385174942398</v>
+      </c>
+      <c r="R15" t="n">
+        <v>99.39100346020761</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.9753562760594935</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H16" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>512</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4515.29</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5542372299716455</v>
+      </c>
+      <c r="N16" t="n">
+        <v>45.51633986928105</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.992891116171589</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.006155324875048059</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>22.10749020276573</v>
+      </c>
+      <c r="R16" t="n">
+        <v>99.38446751249519</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.9750089755397031</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H17" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>512</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4500.94</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.554250768935025</v>
+      </c>
+      <c r="N17" t="n">
+        <v>45.65205690119185</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9928917269466757</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.006013071895424837</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>22.20903603472043</v>
+      </c>
+      <c r="R17" t="n">
+        <v>99.39869281045752</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.975697681645845</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>512</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4504.12</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5542063899702038</v>
+      </c>
+      <c r="N18" t="n">
+        <v>45.87850826605152</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9928992220217001</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.006339869281045751</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21.97919696551354</v>
+      </c>
+      <c r="R18" t="n">
+        <v>99.36601307189542</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.97454657713977</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H19" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>512</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4502.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5542680774822184</v>
+      </c>
+      <c r="N19" t="n">
+        <v>45.52018454440599</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.9928772812395871</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.006301422529796232</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22.00561398625373</v>
+      </c>
+      <c r="R19" t="n">
+        <v>99.36985774702038</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.9745832364115686</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H20" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>512</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4460.92</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5542011260693003</v>
+      </c>
+      <c r="N20" t="n">
+        <v>45.69973087274125</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.9928848860446785</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.006116878123798539</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>22.13470172549291</v>
+      </c>
+      <c r="R20" t="n">
+        <v>99.38831218762014</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9750505731625084</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H21" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>512</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4462.55</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5542172406646482</v>
+      </c>
+      <c r="N21" t="n">
+        <v>45.69742406766628</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.9928848051135363</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.00602076124567474</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>22.20348594473948</v>
+      </c>
+      <c r="R21" t="n">
+        <v>99.39792387543253</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.975669628985147</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H22" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4435.56</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.554251330242575</v>
+      </c>
+      <c r="N22" t="n">
+        <v>47.11880046136102</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.9951871619574508</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.003333333333333334</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>24.77121254719663</v>
+      </c>
+      <c r="R22" t="n">
+        <v>99.66666666666667</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.986458414681765</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H23" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4563.83</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.5542373313449154</v>
+      </c>
+      <c r="N23" t="n">
+        <v>47.20915032679738</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.9951760945424155</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.003160322952710496</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>25.00268534655822</v>
+      </c>
+      <c r="R23" t="n">
+        <v>99.68396770472894</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.9871638714513258</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H24" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4688.47</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5542405752895521</v>
+      </c>
+      <c r="N24" t="n">
+        <v>47.01883890811227</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.9951849342858687</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.003487120338331411</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>24.57533065135777</v>
+      </c>
+      <c r="R24" t="n">
+        <v>99.65128796616686</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.9858154919224935</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H25" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4698.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.554240207342128</v>
+      </c>
+      <c r="N25" t="n">
+        <v>46.96462898885044</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9951860822204753</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.003298731257208766</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>24.81653064347167</v>
+      </c>
+      <c r="R25" t="n">
+        <v>99.67012687427912</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.9866592032838885</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H26" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4691.29</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5542629844140475</v>
+      </c>
+      <c r="N26" t="n">
+        <v>47.02191464821222</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.9951804033711291</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.003133410226835832</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>25.03982743455896</v>
+      </c>
+      <c r="R26" t="n">
+        <v>99.68665897731641</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.9872959955107321</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H27" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4708.29</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5542125831260813</v>
+      </c>
+      <c r="N27" t="n">
+        <v>47.0557477893118</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.9951911018420843</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.003383314109957708</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>24.70657680045704</v>
+      </c>
+      <c r="R27" t="n">
+        <v>99.66166858900422</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.9861865444385144</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H28" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4729.52</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5542194389627787</v>
+      </c>
+      <c r="N28" t="n">
+        <v>47.07881584006152</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.9951802222685165</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.003498654363706267</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>24.56098959874779</v>
+      </c>
+      <c r="R28" t="n">
+        <v>99.65013456362938</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.9856981203243855</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H29" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4735.55</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5542126413218473</v>
+      </c>
+      <c r="N29" t="n">
+        <v>47.19454056132257</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.9951725743802865</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.004071510957324106</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23.90244392088388</v>
+      </c>
+      <c r="R29" t="n">
+        <v>99.5928489042676</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.9836495854498294</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H30" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4733.15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5542364584084246</v>
+      </c>
+      <c r="N30" t="n">
+        <v>47.17954632833526</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.9951777840461615</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.003398692810457516</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>24.686880871828</v>
+      </c>
+      <c r="R30" t="n">
+        <v>99.66013071895425</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.9861159101617716</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H31" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4724.54</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5542237116583766</v>
+      </c>
+      <c r="N31" t="n">
+        <v>46.91657054978855</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.9951792494469425</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.003410226835832372</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>24.67216732364146</v>
+      </c>
+      <c r="R31" t="n">
+        <v>99.65897731641677</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.9862525379333861</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H32" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4703.17</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.5542524002937572</v>
+      </c>
+      <c r="N32" t="n">
+        <v>47.35640138408305</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9955793556686729</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.00249519415609381</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>26.02895655395503</v>
+      </c>
+      <c r="R32" t="n">
+        <v>99.75048058439062</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.9899131191619651</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H33" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4609.48</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.5542301038062284</v>
+      </c>
+      <c r="N33" t="n">
+        <v>47.25374855824683</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.9955846851116448</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.002368319876970396</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>26.25559640031447</v>
+      </c>
+      <c r="R33" t="n">
+        <v>99.76316801230296</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.9903837147585001</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H34" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4575.38</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.554227380807562</v>
+      </c>
+      <c r="N34" t="n">
+        <v>47.33141099577086</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.9955825020376196</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.00251441753171857</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>25.99562603871605</v>
+      </c>
+      <c r="R34" t="n">
+        <v>99.74855824682814</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.9897414983059355</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H35" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4573.89</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.5542342488465974</v>
+      </c>
+      <c r="N35" t="n">
+        <v>47.45520953479431</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9955805013022246</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.002268358323721646</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>26.44288340553728</v>
+      </c>
+      <c r="R35" t="n">
+        <v>99.77316416762784</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.9907685567655526</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H36" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4555.72</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.5542294674073673</v>
+      </c>
+      <c r="N36" t="n">
+        <v>47.51018838908112</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.9955821068036446</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.002722029988465975</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>25.65107094506104</v>
+      </c>
+      <c r="R36" t="n">
+        <v>99.72779700115341</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.9888707243460765</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H37" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>4567.52</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5542434841392133</v>
+      </c>
+      <c r="N37" t="n">
+        <v>47.29373317954633</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.9955799592366045</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.002583621683967705</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>25.87771079142048</v>
+      </c>
+      <c r="R37" t="n">
+        <v>99.74163783160323</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.9894382799484488</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H38" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4542.95</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.5542375631893383</v>
+      </c>
+      <c r="N38" t="n">
+        <v>47.24951941560938</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.9955858077170685</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.002787389465590157</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>25.54802345624879</v>
+      </c>
+      <c r="R38" t="n">
+        <v>99.72126105344098</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.9885950699240196</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H39" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4531.97</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.5542393832149894</v>
+      </c>
+      <c r="N39" t="n">
+        <v>47.27643214148404</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.9955795158444669</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.002299115724721261</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>26.38439168207462</v>
+      </c>
+      <c r="R39" t="n">
+        <v>99.77008842752787</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.9906357657375509</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H40" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4531.42</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.5542437769953263</v>
+      </c>
+      <c r="N40" t="n">
+        <v>47.38946559015763</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.9955785137082348</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.002664359861591695</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>25.74407117584066</v>
+      </c>
+      <c r="R40" t="n">
+        <v>99.73356401384082</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.9891118198815341</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H41" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4537.08</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5542353404865317</v>
+      </c>
+      <c r="N41" t="n">
+        <v>47.36639753940792</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.9955762207698631</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.002572087658592849</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>25.8971423442805</v>
+      </c>
+      <c r="R41" t="n">
+        <v>99.74279123414071</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.9895070345216995</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H42" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>4543.83</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.5542433142451221</v>
+      </c>
+      <c r="N42" t="n">
+        <v>47.39561707035755</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9957842818689664</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.002825836216839677</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>25.48853013111678</v>
+      </c>
+      <c r="R42" t="n">
+        <v>99.71741637831603</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.988631266337721</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H43" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4537.97</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.554240762548509</v>
+      </c>
+      <c r="N43" t="n">
+        <v>47.50557477893118</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.9957873440617203</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.002387543252595156</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>26.22048752019293</v>
+      </c>
+      <c r="R43" t="n">
+        <v>99.76124567474048</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.9903734362647072</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H44" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>4535.34</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.5542443688087214</v>
+      </c>
+      <c r="N44" t="n">
+        <v>47.54133025759323</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.9957901009972444</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.001664744329104191</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>27.78652455842508</v>
+      </c>
+      <c r="R44" t="n">
+        <v>99.83352556708958</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.9932378617275467</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H45" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" t="n">
+        <v>4493.47</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.5542330680357315</v>
+      </c>
+      <c r="N45" t="n">
+        <v>47.55094194540561</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.9957855093397608</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.001918492887351019</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>27.17039806572483</v>
+      </c>
+      <c r="R45" t="n">
+        <v>99.8081507112649</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.992171198167527</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H46" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4468.17</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.5542256945383086</v>
+      </c>
+      <c r="N46" t="n">
+        <v>47.48212226066897</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.9957864994033527</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.002168396770472895</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>26.6386124821253</v>
+      </c>
+      <c r="R46" t="n">
+        <v>99.78316032295271</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.9911354205960015</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H47" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>4495.36</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.554231760508278</v>
+      </c>
+      <c r="N47" t="n">
+        <v>47.45174932718185</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.9957855164035903</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.00239523260284506</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>26.20652305536703</v>
+      </c>
+      <c r="R47" t="n">
+        <v>99.7604767397155</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.9903466228675024</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H48" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4461.58</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.5542345093195826</v>
+      </c>
+      <c r="N48" t="n">
+        <v>47.44252210688197</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.9957890601628052</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.001830065359477124</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>27.3753339947538</v>
+      </c>
+      <c r="R48" t="n">
+        <v>99.81699346405229</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.9925431588181847</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H49" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K49" t="n">
+        <v>7</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4455.89</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.5542464563471682</v>
+      </c>
+      <c r="N49" t="n">
+        <v>47.34294502114572</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.9957869766454459</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.002033833141099577</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>26.91684680160687</v>
+      </c>
+      <c r="R49" t="n">
+        <v>99.79661668589004</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.9917119714227521</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H50" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K50" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" t="n">
+        <v>4449.87</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.5542282814339737</v>
+      </c>
+      <c r="N50" t="n">
+        <v>47.77047289504036</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.9957887074764367</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.001906958861976163</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>27.19658675705675</v>
+      </c>
+      <c r="R50" t="n">
+        <v>99.80930411380238</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.992263297457495</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>127.51171875</v>
+      </c>
+      <c r="H51" t="n">
+        <v>31981</v>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K51" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4444.83</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.5542461850798071</v>
+      </c>
+      <c r="N51" t="n">
+        <v>47.47558631295655</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.9957834276643963</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.002783544790465206</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>25.55401785998726</v>
+      </c>
+      <c r="R51" t="n">
+        <v>99.72164552095349</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.988801237432328</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>run_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>operator</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>remove_dc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>noise_snr</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>shots</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>n_seeds</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dir_acc_pct_mean</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dir_acc_pct_std</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>cos_sim_median_mean</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>cos_sim_median_std</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mag_mse_mean</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>mag_mse_std</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mag_psnr_mean</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>mag_psnr_std</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>accuracy_pct_mean</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>accuracy_pct_std</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>f1_score_mean</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>f1_score_std</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>post_selection_mean_mean</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>post_selection_mean_std</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20261007_084202</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" t="n">
+        <v>46.55286428296809</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.06782926615937526</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9943997859611333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.377884867634883e-06</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.004549404075355633</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.643339324756929e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>23.42124147064381</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0827315216726274</v>
+      </c>
+      <c r="S2" t="n">
+        <v>99.54505959246443</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.008643339324757108</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.9815716525140303</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0002885918538844002</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5542272045307093</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.934371890896847e-05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>512</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
+        <v>45.67577854671281</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1122189542205412</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9928889436470933</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.078274891806155e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.006158785082660515</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.000109278761430211</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>22.1057305113733</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.07683559117418369</v>
+      </c>
+      <c r="S3" t="n">
+        <v>99.38412149173395</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.01092787614302128</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.9750595257288737</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.0004088459646016704</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.5542270656117839</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.475719965593317e-05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>46.55286428296809</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06782926615937575</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9943997859611333</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.377884867634883e-06</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.004549404075355633</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.643339324756929e-05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23.42124147064381</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.08273152167262696</v>
+      </c>
+      <c r="S4" t="n">
+        <v>99.54505959246443</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.008643339324757108</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9815716525140303</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0002885918538844002</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5542272045307093</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.934371890896847e-05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2048</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47.07585544021531</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.09421588785871178</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9951815608361333</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.362847571339843e-06</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.003417531718569781</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0002467338046927801</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>24.67346451387015</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2984396861994831</v>
+      </c>
+      <c r="S5" t="n">
+        <v>99.65824682814302</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.02467338046927413</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.9861295675158092</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0009629459603360807</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5542337262110726</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.572049783159353e-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4096</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>47.34825067281815</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08176220301784753</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9955809168200045</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.745309672264715e-06</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.002527489427143406</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0001658673233997626</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25.98254727934489</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2870735145161215</v>
+      </c>
+      <c r="S6" t="n">
+        <v>99.74725105728564</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.01658673233997632</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9896965583351282</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.000699443913387574</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5542373149186911</v>
+      </c>
+      <c r="X6" t="n">
+        <v>7.330041380219442e-06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261008_083024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8192</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
+        <v>47.4958861976163</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1092841448209904</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9957867424023717</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.026199156999792e-06</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.002191464821222607</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0003770722827883067</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>26.65538612263566</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.7341496694714915</v>
+      </c>
+      <c r="S7" t="n">
+        <v>99.78085351787773</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.03770722827882984</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.9911215471091767</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.001483220640838734</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5542374400865203</v>
+      </c>
+      <c r="X7" t="n">
+        <v>7.301508057625507e-06</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261012_090147</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>512</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>45.67577854671281</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1122189542205412</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.9928889436470933</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.078274891806155e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.006158785082660515</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0001092787614302109</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>22.1057305113733</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.07683559117418327</v>
+      </c>
+      <c r="S8" t="n">
+        <v>99.38412149173395</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.01092787614302128</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.9750595257288737</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0004088459646016704</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5542270656117839</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.475719965593317e-05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261012_090147</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46.55286428296809</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.06782926615937575</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9943997859611333</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.377884867634883e-06</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.004549404075355633</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.643339324756929e-05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23.42124147064381</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.08273152167262696</v>
+      </c>
+      <c r="S9" t="n">
+        <v>99.54505959246443</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.008643339324757108</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9815716525140303</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0002885918538844002</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5542272045307093</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.934371890896847e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261012_090147</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2048</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>47.07585544021531</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.09421588785871035</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9951815608361333</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.362847571339843e-06</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003417531718569781</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0002467338046927801</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>24.67346451387014</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2984396861994815</v>
+      </c>
+      <c r="S10" t="n">
+        <v>99.65824682814302</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.02467338046927413</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.9861295675158092</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.0009629459603360807</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.5542337262110726</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.572049783159353e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261012_090147</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4096</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>47.34825067281814</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.08176220301784691</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.9955809168200045</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.745309672264715e-06</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.002527489427143406</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0001658673233997624</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>25.98254727934489</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2870735145161198</v>
+      </c>
+      <c r="S11" t="n">
+        <v>99.74725105728564</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.01658673233997632</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.9896965583351282</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.000699443913387574</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5542373149186911</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.330041380219442e-06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261012_090147</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pirate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>noisy</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>otsu</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8192</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>47.4958861976163</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1092841448209904</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9957867424023717</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.026199156999792e-06</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.002191464821222607</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0003770722827883066</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>26.65538612263566</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7341496694714921</v>
+      </c>
+      <c r="S12" t="n">
+        <v>99.78085351787773</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.03770722827882984</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.9911215471091767</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.001483220640838734</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5542374400865203</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7.301508057625507e-06</v>
       </c>
     </row>
   </sheetData>
